--- a/Avaliações dos Itens/Pré-teste (2003 - 2007)/2004.xlsx
+++ b/Avaliações dos Itens/Pré-teste (2003 - 2007)/2004.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30CB0950-B0E6-48D8-BF3D-DE5FBAE875DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{F2487550-9290-47F2-B399-67CFEBB20DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A0D3F87F-C85A-48C5-9B60-AA2080D4234A}"/>
+    <workbookView xWindow="30252" yWindow="783" windowWidth="22118" windowHeight="11613" xr2:uid="{A0D3F87F-C85A-48C5-9B60-AA2080D4234A}"/>
   </bookViews>
   <sheets>
     <sheet name="2004" sheetId="1" r:id="rId1"/>
@@ -481,9 +476,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B8D077-0285-4C6F-B686-B2E7E0C89202}">
   <dimension ref="A1:F90"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -503,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,7 +538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,7 +558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,7 +598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,7 +618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,7 +638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,7 +658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,7 +678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,7 +698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,7 +738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -783,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -803,7 +798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
@@ -823,7 +818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -843,7 +838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,7 +858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -883,7 +878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -903,203 +898,203 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -1108,5 +1103,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>